--- a/parameters_CCM.xlsx
+++ b/parameters_CCM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rodemann/Algal_EDM/Algal_blooms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93072D46-C672-4E44-A9EE-ACBD5051FB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F264AE-EF8E-2A43-8617-C9E275B72B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" activeTab="4" xr2:uid="{96C955FB-9A51-4D0B-AF49-129559A448B6}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="6" xr2:uid="{96C955FB-9A51-4D0B-AF49-129559A448B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Run1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="184">
   <si>
     <t>Variable</t>
   </si>
@@ -573,6 +573,27 @@
   </si>
   <si>
     <t>jnh4</t>
+  </si>
+  <si>
+    <t>gargrabchl</t>
+  </si>
+  <si>
+    <t>wbwinddir</t>
+  </si>
+  <si>
+    <t>wbwindspeed</t>
+  </si>
+  <si>
+    <t>gargrab</t>
+  </si>
+  <si>
+    <t>gtnload</t>
+  </si>
+  <si>
+    <t>gtpload</t>
+  </si>
+  <si>
+    <t>gdocload</t>
   </si>
 </sst>
 </file>
@@ -588,7 +609,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -607,6 +628,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -620,10 +653,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2057,7 +2093,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0219A31A-9904-40E1-98EE-E1AAB97C02AB}">
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.1640625" customWidth="1"/>
@@ -3153,6 +3189,57 @@
       </c>
       <c r="E64" s="1" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B65" s="1">
+        <v>1</v>
+      </c>
+      <c r="C65" s="1">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1">
+        <v>2</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B66" s="1">
+        <v>3</v>
+      </c>
+      <c r="C66" s="1">
+        <v>4</v>
+      </c>
+      <c r="D66" s="1">
+        <v>3</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B67" s="1">
+        <v>2</v>
+      </c>
+      <c r="C67" s="1">
+        <v>2</v>
+      </c>
+      <c r="D67" s="1">
+        <v>3</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3373,7 +3460,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4796A85C-8317-4493-888D-443234A7E4BB}">
-  <dimension ref="A1:G237"/>
+  <dimension ref="A1:G268"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="16.83203125" customWidth="1"/>
@@ -4583,38 +4670,38 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>4</v>
-      </c>
-      <c r="B62" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62">
-        <v>0.111</v>
-      </c>
-      <c r="D62">
-        <v>-12</v>
-      </c>
-      <c r="E62" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>4</v>
-      </c>
-      <c r="B63" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63">
-        <v>0.38</v>
-      </c>
-      <c r="D63">
-        <v>-12</v>
-      </c>
-      <c r="E63" t="s">
-        <v>21</v>
+    <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C62" s="2">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="D62" s="2">
+        <v>12</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C63" s="3">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="D63" s="3">
+        <v>0</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
@@ -4622,10 +4709,10 @@
         <v>4</v>
       </c>
       <c r="B64" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C64">
-        <v>0.28499999999999998</v>
+        <v>0.111</v>
       </c>
       <c r="D64">
         <v>-12</v>
@@ -4634,27 +4721,21 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C65" s="1">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="D65" s="1">
-        <v>6</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>72</v>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65">
+        <v>0.38</v>
+      </c>
+      <c r="D65">
+        <v>-12</v>
+      </c>
+      <c r="E65" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -4662,79 +4743,73 @@
         <v>4</v>
       </c>
       <c r="B66" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="D66">
+        <v>-12</v>
+      </c>
+      <c r="E66" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="1">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="D67" s="1">
+        <v>6</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" t="s">
         <v>31</v>
       </c>
-      <c r="C66">
+      <c r="C68">
         <v>0.16800000000000001</v>
       </c>
-      <c r="D66">
+      <c r="D68">
         <v>5</v>
       </c>
-      <c r="E66" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>4</v>
-      </c>
-      <c r="B67" t="s">
+      <c r="E68" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" t="s">
         <v>68</v>
       </c>
-      <c r="C67">
+      <c r="C69">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="D67">
+      <c r="D69">
         <v>2</v>
       </c>
-      <c r="E67" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C68" s="1">
-        <v>0.223</v>
-      </c>
-      <c r="D68" s="1">
-        <v>-4</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C69" s="1">
-        <v>0.47</v>
-      </c>
-      <c r="D69" s="1">
-        <v>-4</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>6</v>
+      <c r="E69" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -4742,102 +4817,102 @@
         <v>4</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C70" s="1">
+        <v>0.223</v>
+      </c>
+      <c r="D70" s="1">
+        <v>-4</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="D71" s="1">
+        <v>-4</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C72" s="1">
         <v>0.6</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D72" s="1">
         <v>7</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>4</v>
-      </c>
-      <c r="B71" t="s">
+      <c r="E72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>4</v>
+      </c>
+      <c r="B73" t="s">
         <v>28</v>
       </c>
-      <c r="C71">
+      <c r="C73">
         <v>0.192</v>
       </c>
-      <c r="D71">
+      <c r="D73">
         <v>5</v>
       </c>
-      <c r="E71" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>4</v>
-      </c>
-      <c r="B72" t="s">
+      <c r="E73" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" t="s">
         <v>27</v>
       </c>
-      <c r="C72">
+      <c r="C74">
         <v>-0.154</v>
       </c>
-      <c r="D72">
+      <c r="D74">
         <v>9</v>
       </c>
-      <c r="E72" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C73" s="1">
-        <v>0.496</v>
-      </c>
-      <c r="D73" s="1">
-        <v>-8</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" s="1">
-        <v>0.45600000000000002</v>
-      </c>
-      <c r="D74" s="1">
-        <v>8</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>6</v>
+      <c r="E74" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -4845,78 +4920,84 @@
         <v>4</v>
       </c>
       <c r="B75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" s="1">
+        <v>0.496</v>
+      </c>
+      <c r="D75" s="1">
+        <v>-8</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="1">
+        <v>0.45600000000000002</v>
+      </c>
+      <c r="D76" s="1">
+        <v>8</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C77" s="1">
         <v>0.73</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D77" s="1">
         <v>-10</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>4</v>
-      </c>
-      <c r="B76" t="s">
+      <c r="E77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
         <v>59</v>
       </c>
-      <c r="C76">
+      <c r="C78">
         <v>-0.13600000000000001</v>
       </c>
-      <c r="D76">
+      <c r="D78">
         <v>9</v>
       </c>
-      <c r="E76" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>4</v>
-      </c>
-      <c r="B77" t="s">
-        <v>53</v>
-      </c>
-      <c r="C77">
-        <v>0.39800000000000002</v>
-      </c>
-      <c r="D77">
-        <v>9</v>
-      </c>
-      <c r="E77" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C78" s="1">
-        <v>0.503</v>
-      </c>
-      <c r="D78" s="1">
-        <v>-12</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G78" s="1" t="s">
+      <c r="E78" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4925,55 +5006,55 @@
         <v>4</v>
       </c>
       <c r="B79" t="s">
+        <v>53</v>
+      </c>
+      <c r="C79">
+        <v>0.39800000000000002</v>
+      </c>
+      <c r="D79">
+        <v>9</v>
+      </c>
+      <c r="E79" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C80" s="1">
+        <v>0.503</v>
+      </c>
+      <c r="D80" s="1">
+        <v>-12</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>4</v>
+      </c>
+      <c r="B81" t="s">
         <v>55</v>
       </c>
-      <c r="C79">
+      <c r="C81">
         <v>0.313</v>
       </c>
-      <c r="D79">
+      <c r="D81">
         <v>7</v>
       </c>
-      <c r="E79" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>4</v>
-      </c>
-      <c r="B80" t="s">
-        <v>56</v>
-      </c>
-      <c r="C80">
-        <v>0.24099999999999999</v>
-      </c>
-      <c r="D80">
-        <v>5</v>
-      </c>
-      <c r="E80" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C81" s="1">
-        <v>0.29199999999999998</v>
-      </c>
-      <c r="D81" s="1">
-        <v>1</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G81" s="1" t="s">
+      <c r="E81" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4982,56 +5063,56 @@
         <v>4</v>
       </c>
       <c r="B82" t="s">
+        <v>56</v>
+      </c>
+      <c r="C82">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="D82">
+        <v>5</v>
+      </c>
+      <c r="E82" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C83" s="1">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="D83" s="1">
+        <v>1</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>4</v>
+      </c>
+      <c r="B84" t="s">
         <v>58</v>
       </c>
-      <c r="C82">
+      <c r="C84">
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="D82">
+      <c r="D84">
         <v>-1</v>
       </c>
-      <c r="E82" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>4</v>
-      </c>
-      <c r="B83" t="s">
-        <v>24</v>
-      </c>
-      <c r="C83">
-        <v>0.25900000000000001</v>
-      </c>
-      <c r="D83">
-        <v>-5</v>
-      </c>
-      <c r="E83" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C84" s="1">
-        <v>0.63600000000000001</v>
-      </c>
-      <c r="D84" s="1">
-        <v>7</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>6</v>
+      <c r="E84" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
@@ -5039,33 +5120,39 @@
         <v>4</v>
       </c>
       <c r="B85" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C85">
-        <v>5.8999999999999997E-2</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E85" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>4</v>
-      </c>
-      <c r="B86" t="s">
-        <v>33</v>
-      </c>
-      <c r="C86">
-        <v>0.32900000000000001</v>
-      </c>
-      <c r="D86">
-        <v>-4</v>
-      </c>
-      <c r="E86" t="s">
-        <v>21</v>
+    <row r="86" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C86" s="1">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="D86" s="1">
+        <v>7</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
@@ -5073,10 +5160,10 @@
         <v>4</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C87">
-        <v>6.7000000000000004E-2</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -5090,106 +5177,106 @@
         <v>4</v>
       </c>
       <c r="B88" t="s">
+        <v>33</v>
+      </c>
+      <c r="C88">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="D88">
+        <v>-4</v>
+      </c>
+      <c r="E88" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>4</v>
+      </c>
+      <c r="B89" t="s">
+        <v>34</v>
+      </c>
+      <c r="C89">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>4</v>
+      </c>
+      <c r="B90" t="s">
         <v>69</v>
       </c>
-      <c r="C88">
+      <c r="C90">
         <v>-3.3000000000000002E-2</v>
       </c>
-      <c r="D88">
-        <v>4</v>
-      </c>
-      <c r="E88" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B89" s="1" t="s">
+      <c r="D90">
+        <v>4</v>
+      </c>
+      <c r="E90" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C89" s="1">
+      <c r="C91" s="1">
         <v>0.14000000000000001</v>
       </c>
-      <c r="D89" s="1">
+      <c r="D91" s="1">
         <v>-2</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B90" s="2" t="s">
+      <c r="E91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C90" s="2">
+      <c r="C92" s="2">
         <v>0.161</v>
       </c>
-      <c r="D90" s="2">
+      <c r="D92" s="2">
         <v>8</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>4</v>
-      </c>
-      <c r="B91" s="2" t="s">
+      <c r="E92" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>4</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C91">
+      <c r="C93">
         <v>0</v>
       </c>
-      <c r="D91">
+      <c r="D93">
         <v>0</v>
       </c>
-      <c r="E91" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>4</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C92">
-        <v>0</v>
-      </c>
-      <c r="D92">
-        <v>0</v>
-      </c>
-      <c r="E92" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C93" s="2">
-        <v>0</v>
-      </c>
-      <c r="D93" s="2">
-        <v>0</v>
-      </c>
-      <c r="E93" s="2" t="s">
+      <c r="E93" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5198,7 +5285,7 @@
         <v>4</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -5215,13 +5302,13 @@
         <v>4</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C95" s="2">
-        <v>0.245</v>
+        <v>0</v>
       </c>
       <c r="D95" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>21</v>
@@ -5232,7 +5319,7 @@
         <v>4</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -5244,185 +5331,185 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
+    <row r="97" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C97" s="2">
+        <v>0.245</v>
+      </c>
+      <c r="D97" s="2">
+        <v>6</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>4</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>4</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C99" s="2">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D99" s="2">
         <v>7</v>
       </c>
-      <c r="E97" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>4</v>
-      </c>
-      <c r="B98" s="2" t="s">
+      <c r="E99" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>4</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C98">
+      <c r="C100">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="D98">
+      <c r="D100">
         <v>-9</v>
       </c>
-      <c r="E98" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B99" s="2" t="s">
+      <c r="E100" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C99" s="2">
+      <c r="C101" s="2">
         <v>0.11700000000000001</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D101" s="2">
         <v>12</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B100" s="2" t="s">
+      <c r="E101" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C100" s="2">
+      <c r="C102" s="2">
         <v>0.215</v>
       </c>
-      <c r="D100" s="2">
+      <c r="D102" s="2">
         <v>9</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B101" s="2" t="s">
+      <c r="E102" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C101" s="2">
+      <c r="C103" s="2">
         <v>0.13300000000000001</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D103" s="2">
         <v>9</v>
       </c>
-      <c r="E101" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B102" s="2" t="s">
+      <c r="E103" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C102" s="2">
+      <c r="C104" s="2">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D104" s="2">
         <v>-4</v>
       </c>
-      <c r="E102" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B103" s="2" t="s">
+      <c r="E104" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C103" s="2">
+      <c r="C105" s="2">
         <v>0.254</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D105" s="2">
         <v>8</v>
       </c>
-      <c r="E103" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B104" s="2" t="s">
+      <c r="E105" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C104" s="2">
+      <c r="C106" s="2">
         <v>0.217</v>
       </c>
-      <c r="D104" s="2">
+      <c r="D106" s="2">
         <v>8</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B105" s="2" t="s">
+      <c r="E106" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C105" s="2">
+      <c r="C107" s="2">
         <v>0.14799999999999999</v>
-      </c>
-      <c r="D105" s="2">
-        <v>9</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C106" s="2">
-        <v>0</v>
-      </c>
-      <c r="D106" s="2">
-        <v>0</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C107" s="2">
-        <v>0.33</v>
       </c>
       <c r="D107" s="2">
         <v>9</v>
@@ -5431,49 +5518,49 @@
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B108" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C108" s="2">
+        <v>0</v>
+      </c>
+      <c r="D108" s="2">
+        <v>0</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C109" s="2">
+        <v>0.33</v>
+      </c>
+      <c r="D109" s="2">
+        <v>9</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C108" s="2">
+      <c r="C110" s="2">
         <v>0.29099999999999998</v>
-      </c>
-      <c r="D108" s="2">
-        <v>-9</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C109" s="2">
-        <v>0</v>
-      </c>
-      <c r="D109" s="2">
-        <v>0</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C110" s="2">
-        <v>6.2E-2</v>
       </c>
       <c r="D110" s="2">
         <v>-9</v>
@@ -5482,101 +5569,101 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B111" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C111" s="2">
+        <v>0</v>
+      </c>
+      <c r="D111" s="2">
+        <v>0</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C112" s="2">
+        <v>6.2E-2</v>
+      </c>
+      <c r="D112" s="2">
+        <v>-9</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C111" s="2">
+      <c r="C113" s="2">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="D111" s="2">
+      <c r="D113" s="2">
         <v>-12</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="1" t="s">
+      <c r="E113" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C112" s="1">
+      <c r="C114" s="1">
         <v>0.36299999999999999</v>
       </c>
-      <c r="D112" s="1">
+      <c r="D114" s="1">
         <v>-7</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="1" t="s">
+      <c r="E114" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B115" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C113" s="1">
+      <c r="C115" s="1">
         <v>0.38500000000000001</v>
       </c>
-      <c r="D113" s="1">
-        <v>6</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>46</v>
-      </c>
-      <c r="B114" t="s">
-        <v>8</v>
-      </c>
-      <c r="C114">
-        <v>5.8000000000000003E-2</v>
-      </c>
-      <c r="D114">
-        <v>6</v>
-      </c>
-      <c r="E114" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>46</v>
-      </c>
-      <c r="B115" t="s">
-        <v>12</v>
-      </c>
-      <c r="C115">
-        <v>8.6999999999999994E-2</v>
-      </c>
-      <c r="D115">
-        <v>-2</v>
-      </c>
-      <c r="E115" t="s">
-        <v>21</v>
+      <c r="D115" s="1">
+        <v>6</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
@@ -5584,13 +5671,13 @@
         <v>46</v>
       </c>
       <c r="B116" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C116">
-        <v>0.35</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="D116">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E116" t="s">
         <v>21</v>
@@ -5601,10 +5688,10 @@
         <v>46</v>
       </c>
       <c r="B117" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="C117">
-        <v>0.17199999999999999</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="D117">
         <v>-2</v>
@@ -5618,13 +5705,13 @@
         <v>46</v>
       </c>
       <c r="B118" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="C118">
-        <v>0.111</v>
+        <v>0.35</v>
       </c>
       <c r="D118">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E118" t="s">
         <v>21</v>
@@ -5635,10 +5722,10 @@
         <v>46</v>
       </c>
       <c r="B119" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="C119">
-        <v>0.191</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="D119">
         <v>-2</v>
@@ -5647,49 +5734,37 @@
         <v>21</v>
       </c>
     </row>
-    <row r="120" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="1" t="s">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
         <v>46</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C120" s="1">
-        <v>0.47699999999999998</v>
-      </c>
-      <c r="D120" s="1">
-        <v>6</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="1" t="s">
+      <c r="B120" t="s">
+        <v>68</v>
+      </c>
+      <c r="C120">
+        <v>0.111</v>
+      </c>
+      <c r="D120">
+        <v>12</v>
+      </c>
+      <c r="E120" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
         <v>46</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C121" s="1">
-        <v>0.318</v>
-      </c>
-      <c r="D121" s="1">
-        <v>9</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G121" s="1" t="s">
+      <c r="B121" t="s">
+        <v>28</v>
+      </c>
+      <c r="C121">
+        <v>0.191</v>
+      </c>
+      <c r="D121">
+        <v>-2</v>
+      </c>
+      <c r="E121" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5698,55 +5773,67 @@
         <v>46</v>
       </c>
       <c r="B122" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C122" s="1">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="D122" s="1">
+        <v>6</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C123" s="1">
+        <v>0.318</v>
+      </c>
+      <c r="D123" s="1">
+        <v>9</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C122" s="1">
+      <c r="C124" s="1">
         <v>0.51800000000000002</v>
       </c>
-      <c r="D122" s="1">
+      <c r="D124" s="1">
         <v>7</v>
       </c>
-      <c r="E122" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
-        <v>46</v>
-      </c>
-      <c r="B123" t="s">
-        <v>59</v>
-      </c>
-      <c r="C123">
-        <v>0.121</v>
-      </c>
-      <c r="D123">
-        <v>-12</v>
-      </c>
-      <c r="E123" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
-        <v>46</v>
-      </c>
-      <c r="B124" t="s">
-        <v>53</v>
-      </c>
-      <c r="C124">
-        <v>0.36299999999999999</v>
-      </c>
-      <c r="D124">
-        <v>8</v>
-      </c>
-      <c r="E124" t="s">
+      <c r="E124" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G124" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -5755,13 +5842,13 @@
         <v>46</v>
       </c>
       <c r="B125" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C125">
-        <v>0.221</v>
+        <v>0.121</v>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="E125" t="s">
         <v>21</v>
@@ -5772,13 +5859,13 @@
         <v>46</v>
       </c>
       <c r="B126" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C126">
-        <v>0.14399999999999999</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="D126">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E126" t="s">
         <v>21</v>
@@ -5789,13 +5876,13 @@
         <v>46</v>
       </c>
       <c r="B127" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C127">
-        <v>0.189</v>
+        <v>0.221</v>
       </c>
       <c r="D127">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="E127" t="s">
         <v>21</v>
@@ -5806,39 +5893,33 @@
         <v>46</v>
       </c>
       <c r="B128" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C128">
-        <v>0.04</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="D128">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E128" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="129" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="1" t="s">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
         <v>46</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C129" s="1">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="D129" s="1">
-        <v>-3</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>6</v>
+      <c r="B129" t="s">
+        <v>56</v>
+      </c>
+      <c r="C129">
+        <v>0.189</v>
+      </c>
+      <c r="D129">
+        <v>-2</v>
+      </c>
+      <c r="E129" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
@@ -5846,33 +5927,39 @@
         <v>46</v>
       </c>
       <c r="B130" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C130">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E130" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A131" t="s">
+    <row r="131" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B131" t="s">
-        <v>33</v>
-      </c>
-      <c r="C131">
-        <v>0.255</v>
-      </c>
-      <c r="D131">
-        <v>4</v>
-      </c>
-      <c r="E131" t="s">
-        <v>21</v>
+      <c r="B131" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C131" s="1">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="D131" s="1">
+        <v>-3</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
@@ -5880,13 +5967,13 @@
         <v>46</v>
       </c>
       <c r="B132" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C132">
-        <v>2.8000000000000001E-2</v>
+        <v>0.23</v>
       </c>
       <c r="D132">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E132" t="s">
         <v>21</v>
@@ -5897,13 +5984,13 @@
         <v>46</v>
       </c>
       <c r="B133" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="C133">
-        <v>0.26600000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="D133">
-        <v>-11</v>
+        <v>4</v>
       </c>
       <c r="E133" t="s">
         <v>21</v>
@@ -5911,16 +5998,16 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B134" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C134">
-        <v>8.1000000000000003E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E134" t="s">
         <v>21</v>
@@ -5928,16 +6015,16 @@
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B135" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="C135">
-        <v>2.1999999999999999E-2</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="D135">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="E135" t="s">
         <v>21</v>
@@ -5945,36 +6032,36 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B136" t="s">
-        <v>8</v>
+        <v>178</v>
       </c>
       <c r="C136">
-        <v>2.9000000000000001E-2</v>
+        <v>0.06</v>
       </c>
       <c r="D136">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="E136" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
-        <v>58</v>
-      </c>
-      <c r="B137" t="s">
-        <v>12</v>
-      </c>
-      <c r="C137">
-        <v>0.23300000000000001</v>
-      </c>
-      <c r="D137">
-        <v>2</v>
-      </c>
-      <c r="E137" t="s">
-        <v>21</v>
+    <row r="137" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C137" s="3">
+        <v>0.42</v>
+      </c>
+      <c r="D137" s="3">
+        <v>-5</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
@@ -5982,13 +6069,13 @@
         <v>58</v>
       </c>
       <c r="B138" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C138">
-        <v>0.20200000000000001</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="D138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138" t="s">
         <v>21</v>
@@ -5999,39 +6086,33 @@
         <v>58</v>
       </c>
       <c r="B139" t="s">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="C139">
-        <v>0.36499999999999999</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="D139">
-        <v>11</v>
+        <v>-10</v>
       </c>
       <c r="E139" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="140" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="1" t="s">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
         <v>58</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C140" s="1">
-        <v>0.61799999999999999</v>
-      </c>
-      <c r="D140" s="1">
-        <v>-6</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>6</v>
+      <c r="B140" t="s">
+        <v>8</v>
+      </c>
+      <c r="C140">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D140">
+        <v>-3</v>
+      </c>
+      <c r="E140" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
@@ -6039,39 +6120,33 @@
         <v>58</v>
       </c>
       <c r="B141" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C141">
-        <v>0.20699999999999999</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="D141">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E141" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="142" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="1" t="s">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
         <v>58</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C142" s="1">
-        <v>0.35399999999999998</v>
-      </c>
-      <c r="D142" s="1">
+      <c r="B142" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="D142">
         <v>1</v>
       </c>
-      <c r="E142" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>6</v>
+      <c r="E142" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
@@ -6079,56 +6154,56 @@
         <v>58</v>
       </c>
       <c r="B143" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="C143">
-        <v>0.193</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E143" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
+    <row r="144" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B144" t="s">
-        <v>27</v>
-      </c>
-      <c r="C144">
-        <v>0.02</v>
-      </c>
-      <c r="D144">
-        <v>8</v>
-      </c>
-      <c r="E144" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="1" t="s">
+      <c r="B144" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C144" s="1">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="D144" s="1">
+        <v>-6</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
         <v>58</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C145" s="1">
-        <v>0.40699999999999997</v>
-      </c>
-      <c r="D145" s="1">
-        <v>-11</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>6</v>
+      <c r="B145" t="s">
+        <v>22</v>
+      </c>
+      <c r="C145">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="D145">
+        <v>5</v>
+      </c>
+      <c r="E145" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="146" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -6136,13 +6211,13 @@
         <v>58</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C146" s="1">
-        <v>0.27400000000000002</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="D146" s="1">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>6</v>
@@ -6154,27 +6229,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="1" t="s">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
         <v>58</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C147" s="1">
-        <v>0.35</v>
-      </c>
-      <c r="D147" s="1">
-        <v>-10</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>6</v>
+      <c r="B147" t="s">
+        <v>28</v>
+      </c>
+      <c r="C147">
+        <v>0.193</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="E147" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
@@ -6182,67 +6251,85 @@
         <v>58</v>
       </c>
       <c r="B148" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C148">
-        <v>0.13100000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="D148">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E148" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
+    <row r="149" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B149" t="s">
-        <v>53</v>
-      </c>
-      <c r="C149">
-        <v>0.33800000000000002</v>
-      </c>
-      <c r="D149">
+      <c r="B149" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C149" s="1">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="D149" s="1">
         <v>-11</v>
       </c>
-      <c r="E149" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
+      <c r="E149" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B150" t="s">
-        <v>50</v>
-      </c>
-      <c r="C150">
-        <v>0.16300000000000001</v>
-      </c>
-      <c r="D150">
-        <v>-11</v>
-      </c>
-      <c r="E150" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
+      <c r="B150" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" s="1">
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="D150" s="1">
+        <v>-9</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B151" t="s">
-        <v>55</v>
-      </c>
-      <c r="C151">
-        <v>0.17899999999999999</v>
-      </c>
-      <c r="D151">
-        <v>1</v>
-      </c>
-      <c r="E151" t="s">
-        <v>21</v>
+      <c r="B151" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C151" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="D151" s="1">
+        <v>-10</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
@@ -6250,13 +6337,13 @@
         <v>58</v>
       </c>
       <c r="B152" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C152">
-        <v>0.23499999999999999</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="D152">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E152" t="s">
         <v>21</v>
@@ -6267,39 +6354,33 @@
         <v>58</v>
       </c>
       <c r="B153" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C153">
-        <v>0.21299999999999999</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="D153">
-        <v>11</v>
+        <v>-11</v>
       </c>
       <c r="E153" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="154" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="1" t="s">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
         <v>58</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C154" s="1">
-        <v>0.34100000000000003</v>
-      </c>
-      <c r="D154" s="1">
+      <c r="B154" t="s">
+        <v>50</v>
+      </c>
+      <c r="C154">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="D154">
         <v>-11</v>
       </c>
-      <c r="E154" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>6</v>
+      <c r="E154" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
@@ -6307,13 +6388,13 @@
         <v>58</v>
       </c>
       <c r="B155" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C155">
-        <v>0.20899999999999999</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="D155">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E155" t="s">
         <v>21</v>
@@ -6324,39 +6405,33 @@
         <v>58</v>
       </c>
       <c r="B156" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C156">
-        <v>0.156</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="D156">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E156" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="157" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="1" t="s">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
         <v>58</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C157" s="1">
-        <v>0.70399999999999996</v>
-      </c>
-      <c r="D157" s="1">
-        <v>0</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G157" s="1" t="s">
-        <v>6</v>
+      <c r="B157" t="s">
+        <v>46</v>
+      </c>
+      <c r="C157">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="D157">
+        <v>11</v>
+      </c>
+      <c r="E157" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="158" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -6364,13 +6439,13 @@
         <v>58</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="C158" s="1">
-        <v>0.48899999999999999</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="D158" s="1">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>6</v>
@@ -6382,27 +6457,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="1" t="s">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
         <v>58</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C159" s="1">
-        <v>0.73699999999999999</v>
-      </c>
-      <c r="D159" s="1">
-        <v>0</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G159" s="1" t="s">
-        <v>6</v>
+      <c r="B159" t="s">
+        <v>24</v>
+      </c>
+      <c r="C159">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="D159">
+        <v>9</v>
+      </c>
+      <c r="E159" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
@@ -6410,13 +6479,13 @@
         <v>58</v>
       </c>
       <c r="B160" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C160">
-        <v>5.8000000000000003E-2</v>
+        <v>0.156</v>
       </c>
       <c r="D160">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E160" t="s">
         <v>21</v>
@@ -6427,13 +6496,13 @@
         <v>58</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C161" s="1">
-        <v>0.19600000000000001</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="D161" s="1">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>6</v>
@@ -6442,7 +6511,7 @@
         <v>6</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -6450,13 +6519,13 @@
         <v>58</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="C162" s="1">
-        <v>0.376</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="D162" s="1">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>6</v>
@@ -6468,37 +6537,43 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="2" t="s">
+    <row r="163" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C163" s="2">
+      <c r="B163" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C163" s="1">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="D163" s="1">
         <v>0</v>
       </c>
-      <c r="D163" s="2">
-        <v>0</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="2" t="s">
+      <c r="E163" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
         <v>58</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C164" s="2">
-        <v>0.253</v>
-      </c>
-      <c r="D164" s="2">
-        <v>5</v>
-      </c>
-      <c r="E164" s="2" t="s">
+      <c r="B164" t="s">
+        <v>69</v>
+      </c>
+      <c r="C164">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="D164">
+        <v>4</v>
+      </c>
+      <c r="E164" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6507,13 +6582,13 @@
         <v>58</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="C165" s="1">
-        <v>0.188</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="D165" s="1">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>6</v>
@@ -6525,44 +6600,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="166" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="2" t="s">
+    <row r="166" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C166" s="2">
-        <v>0.14599999999999999</v>
-      </c>
-      <c r="D166" s="2">
-        <v>11</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="1" t="s">
+      <c r="B166" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C166" s="1">
+        <v>0.376</v>
+      </c>
+      <c r="D166" s="1">
+        <v>-5</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C167" s="1">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="D167" s="1">
-        <v>-2</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>6</v>
+      <c r="B167" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C167" s="2">
+        <v>0</v>
+      </c>
+      <c r="D167" s="2">
+        <v>0</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="168" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -6570,32 +6645,38 @@
         <v>58</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C168" s="2">
-        <v>0.14899999999999999</v>
+        <v>0.253</v>
       </c>
       <c r="D168" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="169" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="2" t="s">
+    <row r="169" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C169" s="2">
-        <v>0.112</v>
-      </c>
-      <c r="D169" s="2">
-        <v>-3</v>
-      </c>
-      <c r="E169" s="2" t="s">
+      <c r="B169" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C169" s="1">
+        <v>0.188</v>
+      </c>
+      <c r="D169" s="1">
+        <v>-2</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G169" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6604,13 +6685,13 @@
         <v>58</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C170" s="2">
-        <v>0.129</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="D170" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>21</v>
@@ -6621,13 +6702,13 @@
         <v>58</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C171" s="1">
-        <v>0.35199999999999998</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="D171" s="1">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>6</v>
@@ -6639,21 +6720,21 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="1" t="s">
+    <row r="172" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C172" s="1">
-        <v>0.54600000000000004</v>
-      </c>
-      <c r="D172" s="1">
-        <v>-5</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>6</v>
+      <c r="B172" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C172" s="2">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="D172" s="2">
+        <v>12</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="173" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -6661,13 +6742,13 @@
         <v>58</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C173" s="2">
-        <v>0.184</v>
+        <v>0.112</v>
       </c>
       <c r="D173" s="2">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>21</v>
@@ -6678,10 +6759,10 @@
         <v>58</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C174" s="2">
-        <v>0.13900000000000001</v>
+        <v>0.129</v>
       </c>
       <c r="D174" s="2">
         <v>12</v>
@@ -6695,13 +6776,13 @@
         <v>58</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C175" s="1">
-        <v>0.33300000000000002</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="D175" s="1">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>6</v>
@@ -6713,44 +6794,38 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="2" t="s">
+    <row r="176" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B176" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C176" s="2">
-        <v>0.191</v>
-      </c>
-      <c r="D176" s="2">
-        <v>3</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="1" t="s">
+      <c r="B176" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C176" s="1">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="D176" s="1">
+        <v>-5</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C177" s="1">
-        <v>0.219</v>
-      </c>
-      <c r="D177" s="1">
-        <v>-5</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>6</v>
+      <c r="B177" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C177" s="2">
+        <v>0.184</v>
+      </c>
+      <c r="D177" s="2">
+        <v>-7</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="178" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -6758,10 +6833,10 @@
         <v>58</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C178" s="2">
-        <v>0.17199999999999999</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="D178" s="2">
         <v>12</v>
@@ -6775,10 +6850,10 @@
         <v>58</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C179" s="1">
-        <v>0.22</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="D179" s="1">
         <v>-2</v>
@@ -6793,60 +6868,60 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C180" s="2">
-        <v>0.2</v>
+        <v>0.191</v>
       </c>
       <c r="D180" s="2">
+        <v>3</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C181" s="1">
+        <v>0.219</v>
+      </c>
+      <c r="D181" s="1">
+        <v>-5</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C182" s="2">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="D182" s="2">
         <v>12</v>
       </c>
-      <c r="E180" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C181" s="2">
-        <v>0.155</v>
-      </c>
-      <c r="D181" s="2">
-        <v>-5</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C182" s="1">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="D182" s="1">
-        <v>-6</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G182" s="1" t="s">
+      <c r="E182" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6855,13 +6930,13 @@
         <v>58</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C183" s="1">
-        <v>0.53600000000000003</v>
+        <v>0.22</v>
       </c>
       <c r="D183" s="1">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>6</v>
@@ -6873,18 +6948,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>176</v>
+        <v>95</v>
       </c>
       <c r="C184" s="2">
-        <v>0.10199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="D184" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>21</v>
@@ -6895,50 +6970,62 @@
         <v>58</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="C185" s="2">
-        <v>3.5000000000000003E-2</v>
+        <v>0.155</v>
       </c>
       <c r="D185" s="2">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="2" t="s">
+    <row r="186" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B186" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C186" s="2">
-        <v>0.27500000000000002</v>
-      </c>
-      <c r="D186" s="2">
-        <v>4</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="2" t="s">
+      <c r="B186" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C186" s="1">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="D186" s="1">
+        <v>-6</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B187" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C187" s="2">
-        <v>0.124</v>
-      </c>
-      <c r="D187" s="2">
-        <v>-8</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>21</v>
+      <c r="B187" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C187" s="1">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="D187" s="1">
+        <v>-6</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="188" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -6946,38 +7033,32 @@
         <v>58</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C188" s="2">
-        <v>0.246</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="D188" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="189" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="1" t="s">
+    <row r="189" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C189" s="1">
-        <v>0.31</v>
-      </c>
-      <c r="D189" s="1">
-        <v>-8</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G189" s="1" t="s">
+      <c r="B189" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C189" s="2">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="D189" s="2">
+        <v>1</v>
+      </c>
+      <c r="E189" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -6986,13 +7067,13 @@
         <v>58</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C190" s="2">
-        <v>0.107</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="D190" s="2">
-        <v>-8</v>
+        <v>4</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>21</v>
@@ -7003,13 +7084,13 @@
         <v>58</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C191" s="2">
-        <v>0</v>
+        <v>0.124</v>
       </c>
       <c r="D191" s="2">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>21</v>
@@ -7020,263 +7101,266 @@
         <v>58</v>
       </c>
       <c r="B192" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C192" s="2">
+        <v>0.246</v>
+      </c>
+      <c r="D192" s="2">
+        <v>11</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C193" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="D193" s="1">
+        <v>-8</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C194" s="2">
+        <v>0.107</v>
+      </c>
+      <c r="D194" s="2">
+        <v>-8</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C195" s="2">
+        <v>0</v>
+      </c>
+      <c r="D195" s="2">
+        <v>0</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B196" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C192" s="2">
+      <c r="C196" s="2">
         <v>0.187</v>
       </c>
-      <c r="D192" s="2">
+      <c r="D196" s="2">
         <v>-8</v>
       </c>
-      <c r="E192" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="2" t="s">
+      <c r="E196" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B193" s="2" t="s">
+      <c r="B197" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C193" s="2">
+      <c r="C197" s="2">
         <v>0</v>
       </c>
-      <c r="D193" s="2">
+      <c r="D197" s="2">
         <v>0</v>
       </c>
-      <c r="E193" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A194" s="2" t="s">
+      <c r="E197" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A198" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B194" s="2" t="s">
+      <c r="B198" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C194" s="2">
+      <c r="C198" s="2">
         <v>0.30399999999999999</v>
       </c>
-      <c r="D194" s="2">
+      <c r="D198" s="2">
         <v>11</v>
       </c>
-      <c r="E194" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C195" s="1">
-        <v>0.57199999999999995</v>
-      </c>
-      <c r="D195" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C196" s="2">
-        <v>0.24</v>
-      </c>
-      <c r="D196" s="2">
-        <v>5</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C197" s="1">
-        <v>0.439</v>
-      </c>
-      <c r="D197" s="1">
-        <v>-2</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F197" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C198" s="1">
-        <v>0.40699999999999997</v>
-      </c>
-      <c r="D198" s="1">
-        <v>-3</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F198" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E198" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C199" s="1">
-        <v>0.54700000000000004</v>
+        <v>0.57199999999999995</v>
       </c>
       <c r="D199" s="1">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
         <v>175</v>
       </c>
       <c r="B200" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C200" s="2">
+        <v>0.24</v>
+      </c>
+      <c r="D200" s="2">
+        <v>5</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C201" s="1">
+        <v>0.439</v>
+      </c>
+      <c r="D201" s="1">
+        <v>-2</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C202" s="1">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="D202" s="1">
+        <v>-3</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C203" s="1">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="D203" s="1">
+        <v>-2</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A204" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B204" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C200" s="2">
+      <c r="C204" s="2">
         <v>0.11600000000000001</v>
       </c>
-      <c r="D200" s="2">
+      <c r="D204" s="2">
         <v>2</v>
       </c>
-      <c r="E200" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A201" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C201" s="2">
-        <v>0.313</v>
-      </c>
-      <c r="D201" s="2">
-        <v>6</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C202" s="2">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="D202" s="2">
-        <v>-4</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C203" s="2">
-        <v>0</v>
-      </c>
-      <c r="D203" s="2">
-        <v>0</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C204" s="1">
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="D204" s="1">
-        <v>-3</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F204" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E204" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
         <v>175</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C205" s="2">
-        <v>0.29199999999999998</v>
+        <v>0.313</v>
       </c>
       <c r="D205" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
         <v>175</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C206" s="2">
-        <v>0.24099999999999999</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="D206" s="2">
         <v>-4</v>
@@ -7285,152 +7369,152 @@
         <v>21</v>
       </c>
     </row>
-    <row r="207" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="1" t="s">
+    <row r="207" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B207" s="1" t="s">
+      <c r="B207" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C207" s="2">
+        <v>0</v>
+      </c>
+      <c r="D207" s="2">
+        <v>0</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C208" s="1">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="D208" s="1">
+        <v>-3</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A209" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C209" s="2">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="D209" s="2">
+        <v>10</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C210" s="2">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="D210" s="2">
+        <v>-4</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C207" s="1">
+      <c r="C211" s="1">
         <v>0.505</v>
       </c>
-      <c r="D207" s="1">
+      <c r="D211" s="1">
         <v>-6</v>
       </c>
-      <c r="E207" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F207" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="2" t="s">
+      <c r="E211" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F211" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B208" s="2" t="s">
+      <c r="B212" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C208" s="2">
+      <c r="C212" s="2">
         <v>0.161</v>
       </c>
-      <c r="D208" s="2">
-        <v>6</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="1" t="s">
+      <c r="D212" s="2">
+        <v>6</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B209" s="1" t="s">
+      <c r="B213" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C209" s="1">
+      <c r="C213" s="1">
         <v>0.57299999999999995</v>
       </c>
-      <c r="D209" s="1">
+      <c r="D213" s="1">
         <v>-2</v>
       </c>
-      <c r="E209" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F209" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="1" t="s">
+      <c r="E213" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F213" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B210" s="1" t="s">
+      <c r="B214" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C210" s="1">
+      <c r="C214" s="1">
         <v>0.39</v>
       </c>
-      <c r="D210" s="1">
+      <c r="D214" s="1">
         <v>-3</v>
       </c>
-      <c r="E210" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F210" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A211" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C211">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="D211">
-        <v>-6</v>
-      </c>
-      <c r="E211" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C212" s="1">
-        <v>0.51800000000000002</v>
-      </c>
-      <c r="D212" s="1">
-        <v>-12</v>
-      </c>
-      <c r="E212" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F212" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A213" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C213">
-        <v>7.0999999999999994E-2</v>
-      </c>
-      <c r="D213">
-        <v>0</v>
-      </c>
-      <c r="E213" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A214" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C214">
-        <v>0.63900000000000001</v>
-      </c>
-      <c r="D214">
-        <v>0</v>
-      </c>
-      <c r="E214" t="s">
-        <v>21</v>
+      <c r="E214" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F214" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.2">
@@ -7438,73 +7522,70 @@
         <v>175</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>168</v>
+        <v>95</v>
       </c>
       <c r="C215">
-        <v>0.312</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="D215">
+        <v>-6</v>
+      </c>
+      <c r="E215" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C216" s="1">
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="D216" s="1">
         <v>-12</v>
       </c>
-      <c r="E215" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A216" s="2" t="s">
+      <c r="E216" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F216" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A217" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B216" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C216">
-        <v>0.90600000000000003</v>
-      </c>
-      <c r="D216">
+      <c r="B217" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C217">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="D217">
         <v>0</v>
       </c>
-      <c r="E216" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="1" t="s">
+      <c r="E217" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A218" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C217" s="1">
-        <v>0.52900000000000003</v>
-      </c>
-      <c r="D217" s="1">
-        <v>-2</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F217" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A218" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C218" s="1">
-        <v>0.65100000000000002</v>
-      </c>
-      <c r="D218" s="1">
-        <v>-8</v>
-      </c>
-      <c r="E218" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F218" s="1" t="s">
-        <v>6</v>
+      <c r="B218" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C218">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+      <c r="E218" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.2">
@@ -7512,13 +7593,13 @@
         <v>175</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C219">
-        <v>0.85399999999999998</v>
+        <v>0.312</v>
       </c>
       <c r="D219">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E219" t="s">
         <v>21</v>
@@ -7529,13 +7610,13 @@
         <v>175</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C220">
-        <v>0.47899999999999998</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="D220">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E220" t="s">
         <v>21</v>
@@ -7543,16 +7624,16 @@
     </row>
     <row r="221" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>8</v>
+        <v>171</v>
       </c>
       <c r="C221" s="1">
-        <v>0.36499999999999999</v>
+        <v>0.52900000000000003</v>
       </c>
       <c r="D221" s="1">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>6</v>
@@ -7561,75 +7642,78 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A222" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C222">
-        <v>0.32700000000000001</v>
-      </c>
-      <c r="D222">
-        <v>-4</v>
-      </c>
-      <c r="E222" t="s">
-        <v>21</v>
+    <row r="222" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C222" s="1">
+        <v>0.65100000000000002</v>
+      </c>
+      <c r="D222" s="1">
+        <v>-8</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C223">
+        <v>0.85399999999999998</v>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+      <c r="E223" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A224" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C224">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="D224">
+        <v>5</v>
+      </c>
+      <c r="E224" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B223" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C223">
-        <v>0.29299999999999998</v>
-      </c>
-      <c r="D223">
-        <v>-11</v>
-      </c>
-      <c r="E223" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A224" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B224" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C224" s="1">
-        <v>0.34599999999999997</v>
-      </c>
-      <c r="D224" s="1">
-        <v>-6</v>
-      </c>
-      <c r="E224" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F224" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A225" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C225">
-        <v>0.30599999999999999</v>
-      </c>
-      <c r="D225">
-        <v>10</v>
-      </c>
-      <c r="E225" t="s">
-        <v>21</v>
+      <c r="B225" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C225" s="1">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="D225" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.2">
@@ -7637,16 +7721,16 @@
         <v>22</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C226">
-        <v>0.39400000000000002</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="D226">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="E226" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.2">
@@ -7654,32 +7738,35 @@
         <v>22</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C227">
-        <v>0.254</v>
+        <v>0.29299999999999998</v>
       </c>
       <c r="D227">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="E227" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A228" s="2" t="s">
+    <row r="228" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B228" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C228">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="D228">
-        <v>12</v>
-      </c>
-      <c r="E228" t="s">
+      <c r="B228" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C228" s="1">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="D228" s="1">
+        <v>-6</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F228" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -7688,13 +7775,13 @@
         <v>22</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C229">
-        <v>0.46200000000000002</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="D229">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E229" t="s">
         <v>21</v>
@@ -7705,16 +7792,16 @@
         <v>22</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C230">
-        <v>0.31900000000000001</v>
+        <v>0.39400000000000002</v>
       </c>
       <c r="D230">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="E230" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.2">
@@ -7722,13 +7809,13 @@
         <v>22</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C231">
-        <v>0.55000000000000004</v>
+        <v>0.254</v>
       </c>
       <c r="D231">
-        <v>10</v>
+        <v>-12</v>
       </c>
       <c r="E231" t="s">
         <v>21</v>
@@ -7739,13 +7826,13 @@
         <v>22</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C232">
-        <v>0.28599999999999998</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="D232">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="E232" t="s">
         <v>21</v>
@@ -7756,35 +7843,32 @@
         <v>22</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C233">
-        <v>0.16800000000000001</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="D233">
-        <v>-6</v>
+        <v>9</v>
       </c>
       <c r="E233" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="234" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A234" s="1" t="s">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A234" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C234" s="1">
-        <v>0.36699999999999999</v>
-      </c>
-      <c r="D234" s="1">
-        <v>-4</v>
-      </c>
-      <c r="E234" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F234" s="1" t="s">
+      <c r="B234" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C234">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="D234">
+        <v>2</v>
+      </c>
+      <c r="E234" t="s">
         <v>21</v>
       </c>
     </row>
@@ -7793,13 +7877,13 @@
         <v>22</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="C235">
-        <v>7.4999999999999997E-2</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E235" t="s">
         <v>21</v>
@@ -7810,35 +7894,586 @@
         <v>22</v>
       </c>
       <c r="B236" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C236">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="D236">
+        <v>-1</v>
+      </c>
+      <c r="E236" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A237" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C237">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="D237">
+        <v>-6</v>
+      </c>
+      <c r="E237" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C238" s="1">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="D238" s="1">
+        <v>-4</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F238" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A239" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C239">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="D239">
+        <v>0</v>
+      </c>
+      <c r="E239" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A240" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B240" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C236">
+      <c r="C240">
         <v>0</v>
       </c>
-      <c r="D236">
+      <c r="D240">
         <v>0</v>
       </c>
-      <c r="E236" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A237" s="1" t="s">
+      <c r="E240" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A241" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B237" s="1" t="s">
+      <c r="B241" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C237" s="1">
+      <c r="C241" s="1">
         <v>0.27</v>
       </c>
-      <c r="D237" s="1">
+      <c r="D241" s="1">
         <v>-4</v>
       </c>
-      <c r="E237" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F237" s="1" t="s">
+      <c r="E241" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F241" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>180</v>
+      </c>
+      <c r="B242" t="s">
+        <v>11</v>
+      </c>
+      <c r="C242">
+        <v>0.12</v>
+      </c>
+      <c r="D242">
+        <v>-1</v>
+      </c>
+      <c r="E242" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>180</v>
+      </c>
+      <c r="B243" t="s">
+        <v>7</v>
+      </c>
+      <c r="C243">
+        <v>0.21</v>
+      </c>
+      <c r="D243">
+        <v>-6</v>
+      </c>
+      <c r="E243" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>180</v>
+      </c>
+      <c r="B244" t="s">
+        <v>8</v>
+      </c>
+      <c r="C244">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="D244">
+        <v>-1</v>
+      </c>
+      <c r="E244" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A245" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C245" s="3">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="D245" s="3">
+        <v>-1</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A246" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C246" s="3">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="D246" s="3">
+        <v>-3</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>180</v>
+      </c>
+      <c r="B247" t="s">
+        <v>22</v>
+      </c>
+      <c r="C247">
+        <v>0.156</v>
+      </c>
+      <c r="D247">
+        <v>0</v>
+      </c>
+      <c r="E247" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>180</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C248" s="1">
+        <v>0.245</v>
+      </c>
+      <c r="D248" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A249" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C249" s="3">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="D249" s="3">
+        <v>-3</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A250" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C250" s="3">
+        <v>0.443</v>
+      </c>
+      <c r="D250" s="3">
+        <v>-10</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>180</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C251" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="D251" s="1">
+        <v>-4</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>180</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C252" s="1">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="D252" s="1">
+        <v>-4</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A253" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C253" s="3">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="D253" s="3">
+        <v>-1</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A254" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C254" s="3">
+        <v>0.318</v>
+      </c>
+      <c r="D254" s="3">
+        <v>-4</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A255" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C255" s="4">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="D255" s="4">
+        <v>0</v>
+      </c>
+      <c r="E255" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A256" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C256" s="3">
+        <v>0.35899999999999999</v>
+      </c>
+      <c r="D256" s="3">
+        <v>-1</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A257" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C257" s="4">
+        <v>0.22</v>
+      </c>
+      <c r="D257" s="4">
+        <v>-8</v>
+      </c>
+      <c r="E257" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A258" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C258" s="3">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="D258" s="3">
+        <v>-7</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A259" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C259" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D259" s="4">
+        <v>-12</v>
+      </c>
+      <c r="E259" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A260" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C260" s="4">
+        <v>0.06</v>
+      </c>
+      <c r="D260" s="4">
+        <v>0</v>
+      </c>
+      <c r="E260" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A261" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C261" s="4">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="D261" s="4">
+        <v>-10</v>
+      </c>
+      <c r="E261" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A262" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C262" s="4">
+        <v>0.107</v>
+      </c>
+      <c r="D262" s="4">
+        <v>-12</v>
+      </c>
+      <c r="E262" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A263" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C263" s="4">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="D263" s="4">
+        <v>0</v>
+      </c>
+      <c r="E263" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A264" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C264" s="4">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="D264" s="4">
+        <v>-2</v>
+      </c>
+      <c r="E264" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A265" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C265" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="D265" s="4">
+        <v>-5</v>
+      </c>
+      <c r="E265" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A266" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C266" s="4">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D266" s="4">
+        <v>0</v>
+      </c>
+      <c r="E266" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A267" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C267" s="5">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="D267" s="5">
+        <v>-1</v>
+      </c>
+      <c r="E267" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F267" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A268" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C268" s="5">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="D268" s="5">
+        <v>-1</v>
+      </c>
+      <c r="E268" s="5" t="s">
         <v>6</v>
       </c>
     </row>
